--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_18.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4655 +469,6915 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.109</t>
+          <t>2026-05-29 09:42:45.361</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779422064219</v>
+        <v>1780022563805</v>
       </c>
       <c r="C2" t="n">
-        <v>86012</v>
+        <v>81003</v>
       </c>
       <c r="D2" t="n">
-        <v>-91.31</v>
+        <v>594.99</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>725</v>
+        <v>399</v>
       </c>
       <c r="G2" t="n">
-        <v>58.64</v>
+        <v>276.92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L2" t="n">
+        <v>111</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.110</t>
+          <t>2026-05-29 09:42:45.362</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779422064421</v>
+        <v>1780022564005</v>
       </c>
       <c r="C3" t="n">
-        <v>86124</v>
+        <v>81490</v>
       </c>
       <c r="D3" t="n">
-        <v>25.26</v>
+        <v>1052.24</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>766</v>
+        <v>399</v>
       </c>
       <c r="G3" t="n">
-        <v>49.31</v>
+        <v>276.92</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1356</v>
+      </c>
+      <c r="L3" t="n">
+        <v>94</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.883</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.111</t>
+          <t>2026-05-29 09:42:45.363</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779422064622</v>
+        <v>1780022564205</v>
       </c>
       <c r="C4" t="n">
-        <v>85423</v>
+        <v>81818</v>
       </c>
       <c r="D4" t="n">
-        <v>-677</v>
+        <v>1327.63</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>766</v>
+        <v>1240</v>
       </c>
       <c r="G4" t="n">
-        <v>49.31</v>
+        <v>280.47</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L4" t="n">
+        <v>122</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.111</t>
+          <t>2026-05-29 09:42:45.552</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779422064823</v>
+        <v>1780022564425</v>
       </c>
       <c r="C5" t="n">
-        <v>85655</v>
+        <v>82119</v>
       </c>
       <c r="D5" t="n">
-        <v>-411.15</v>
+        <v>1562.24</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>766</v>
+        <v>1240</v>
       </c>
       <c r="G5" t="n">
-        <v>49.31</v>
+        <v>280.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L5" t="n">
+        <v>123</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.112</t>
+          <t>2026-05-29 09:42:45.553</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779422065025</v>
+        <v>1780022564624</v>
       </c>
       <c r="C6" t="n">
-        <v>85862</v>
+        <v>81936</v>
       </c>
       <c r="D6" t="n">
-        <v>-183.6</v>
+        <v>1301.13</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>766</v>
+        <v>1240</v>
       </c>
       <c r="G6" t="n">
-        <v>49.31</v>
+        <v>280.47</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K6" t="n">
+        <v>928</v>
+      </c>
+      <c r="L6" t="n">
+        <v>113</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.971</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.237</t>
+          <t>2026-05-29 09:42:45.574</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779422065226</v>
+        <v>1780022564824</v>
       </c>
       <c r="C7" t="n">
-        <v>86042</v>
+        <v>81612</v>
       </c>
       <c r="D7" t="n">
-        <v>5.58</v>
+        <v>912.08</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>785</v>
+        <v>1240</v>
       </c>
       <c r="G7" t="n">
-        <v>47.23</v>
+        <v>280.47</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>749</v>
+      </c>
+      <c r="L7" t="n">
+        <v>99</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.295</t>
+          <t>2026-05-29 09:42:46.141</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779422065428</v>
+        <v>1780022565024</v>
       </c>
       <c r="C8" t="n">
-        <v>85289</v>
+        <v>81888</v>
       </c>
       <c r="D8" t="n">
-        <v>-747.6900000000001</v>
+        <v>1142.47</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>785</v>
+        <v>1240</v>
       </c>
       <c r="G8" t="n">
-        <v>47.23</v>
+        <v>280.47</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L8" t="n">
+        <v>123</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.676</t>
+          <t>2026-05-29 09:42:46.156</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779422065629</v>
+        <v>1780022565224</v>
       </c>
       <c r="C9" t="n">
-        <v>85471</v>
+        <v>81345</v>
       </c>
       <c r="D9" t="n">
-        <v>-528.3099999999999</v>
+        <v>542.35</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>785</v>
+        <v>1079</v>
       </c>
       <c r="G9" t="n">
-        <v>47.23</v>
+        <v>282.09</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>931</v>
+      </c>
+      <c r="L9" t="n">
+        <v>111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.095</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:23.696</t>
+          <t>2026-05-29 09:42:46.403</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779422065830</v>
+        <v>1780022565424</v>
       </c>
       <c r="C10" t="n">
-        <v>85653</v>
+        <v>81412</v>
       </c>
       <c r="D10" t="n">
-        <v>-319.89</v>
+        <v>582.23</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>785</v>
+        <v>1079</v>
       </c>
       <c r="G10" t="n">
-        <v>47.23</v>
+        <v>282.09</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K10" t="n">
+        <v>978</v>
+      </c>
+      <c r="L10" t="n">
+        <v>120</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:24.304</t>
+          <t>2026-05-29 09:42:46.405</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779422066032</v>
+        <v>1780022565624</v>
       </c>
       <c r="C11" t="n">
-        <v>85830</v>
+        <v>81940</v>
       </c>
       <c r="D11" t="n">
-        <v>-126.9</v>
+        <v>1081.12</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>846</v>
+        <v>1079</v>
       </c>
       <c r="G11" t="n">
-        <v>51.49</v>
+        <v>282.09</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>780</v>
+      </c>
+      <c r="L11" t="n">
+        <v>110</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:24.309</t>
+          <t>2026-05-29 09:42:46.785</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779422066233</v>
+        <v>1780022565824</v>
       </c>
       <c r="C12" t="n">
-        <v>85204</v>
+        <v>81789</v>
       </c>
       <c r="D12" t="n">
-        <v>-746.55</v>
+        <v>876.0599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>846</v>
+        <v>500</v>
       </c>
       <c r="G12" t="n">
-        <v>51.49</v>
+        <v>262.22</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K12" t="n">
+        <v>960</v>
+      </c>
+      <c r="L12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:24.337</t>
+          <t>2026-05-29 09:42:46.787</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779422066435</v>
+        <v>1780022566043</v>
       </c>
       <c r="C13" t="n">
-        <v>85472</v>
+        <v>81463</v>
       </c>
       <c r="D13" t="n">
-        <v>-441.23</v>
+        <v>506.26</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>846</v>
+        <v>500</v>
       </c>
       <c r="G13" t="n">
-        <v>51.49</v>
+        <v>262.22</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>743</v>
+      </c>
+      <c r="L13" t="n">
+        <v>105</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:24.687</t>
+          <t>2026-05-29 09:42:47.247</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779422066636</v>
+        <v>1780022566243</v>
       </c>
       <c r="C14" t="n">
-        <v>85769</v>
+        <v>80290</v>
       </c>
       <c r="D14" t="n">
-        <v>-122.17</v>
+        <v>-692.05</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>846</v>
+        <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>51.49</v>
+        <v>262.22</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L14" t="n">
+        <v>113</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.906</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:24.689</t>
+          <t>2026-05-29 09:42:47.285</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779422066837</v>
+        <v>1780022566443</v>
       </c>
       <c r="C15" t="n">
-        <v>86054</v>
+        <v>80866</v>
       </c>
       <c r="D15" t="n">
-        <v>168.94</v>
+        <v>-81.45</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>705</v>
+        <v>500</v>
       </c>
       <c r="G15" t="n">
-        <v>54.49</v>
+        <v>262.22</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>841</v>
+      </c>
+      <c r="L15" t="n">
+        <v>105</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:25.100</t>
+          <t>2026-05-29 09:42:47.676</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779422067039</v>
+        <v>1780022566643</v>
       </c>
       <c r="C16" t="n">
-        <v>85379</v>
+        <v>82769</v>
       </c>
       <c r="D16" t="n">
-        <v>-514.5</v>
+        <v>1825.62</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>705</v>
+        <v>500</v>
       </c>
       <c r="G16" t="n">
-        <v>54.49</v>
+        <v>262.22</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="L16" t="n">
+        <v>114</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:25.111</t>
+          <t>2026-05-29 09:42:47.701</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779422067240</v>
+        <v>1780022566843</v>
       </c>
       <c r="C17" t="n">
-        <v>85681</v>
+        <v>83181</v>
       </c>
       <c r="D17" t="n">
-        <v>-186.78</v>
+        <v>2146.34</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
-        <v>705</v>
+        <v>500</v>
       </c>
       <c r="G17" t="n">
-        <v>54.49</v>
+        <v>262.22</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>857</v>
+      </c>
+      <c r="L17" t="n">
+        <v>105</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.066</t>
+          <t>2026-05-29 09:42:48.085</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779422067442</v>
+        <v>1780022567043</v>
       </c>
       <c r="C18" t="n">
-        <v>85953</v>
+        <v>82560</v>
       </c>
       <c r="D18" t="n">
-        <v>94.56</v>
+        <v>1418.02</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="G18" t="n">
-        <v>55.35</v>
+        <v>262.22</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L18" t="n">
+        <v>111</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.955</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.073</t>
+          <t>2026-05-29 09:42:48.086</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779422067643</v>
+        <v>1780022567243</v>
       </c>
       <c r="C19" t="n">
-        <v>86265</v>
+        <v>82271</v>
       </c>
       <c r="D19" t="n">
-        <v>401.83</v>
+        <v>1058.12</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F19" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="G19" t="n">
-        <v>55.35</v>
+        <v>262.22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>842</v>
+      </c>
+      <c r="L19" t="n">
+        <v>104</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.073</t>
+          <t>2026-05-29 09:42:48.585</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779422067844</v>
+        <v>1780022567443</v>
       </c>
       <c r="C20" t="n">
-        <v>85490</v>
+        <v>82256</v>
       </c>
       <c r="D20" t="n">
-        <v>-393.26</v>
+        <v>990.22</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="G20" t="n">
-        <v>55.35</v>
+        <v>262.22</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1142</v>
+      </c>
+      <c r="L20" t="n">
+        <v>115</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.868</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.094</t>
+          <t>2026-05-29 09:42:48.587</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779422068046</v>
+        <v>1780022567662</v>
       </c>
       <c r="C21" t="n">
-        <v>85705</v>
+        <v>81875</v>
       </c>
       <c r="D21" t="n">
-        <v>-158.6</v>
+        <v>559.71</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="G21" t="n">
-        <v>55.35</v>
+        <v>262.22</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>924</v>
+      </c>
+      <c r="L21" t="n">
+        <v>117</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.339</t>
+          <t>2026-05-29 09:42:49.648</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779422068247</v>
+        <v>1780022567862</v>
       </c>
       <c r="C22" t="n">
-        <v>85916</v>
+        <v>81088</v>
       </c>
       <c r="D22" t="n">
-        <v>60.33</v>
+        <v>-255.28</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="G22" t="n">
-        <v>55.35</v>
+        <v>262.22</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L22" t="n">
+        <v>109</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.185</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.361</t>
+          <t>2026-05-29 09:42:49.649</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779422068449</v>
+        <v>1780022568062</v>
       </c>
       <c r="C23" t="n">
-        <v>86160</v>
+        <v>81536</v>
       </c>
       <c r="D23" t="n">
-        <v>301.32</v>
+        <v>205.48</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>927</v>
+        <v>500</v>
       </c>
       <c r="G23" t="n">
-        <v>70.59999999999999</v>
+        <v>262.22</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1586</v>
+      </c>
+      <c r="L23" t="n">
+        <v>105</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.038</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.924</t>
+          <t>2026-05-29 09:42:49.891</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779422068650</v>
+        <v>1780022568262</v>
       </c>
       <c r="C24" t="n">
-        <v>85463</v>
+        <v>81603</v>
       </c>
       <c r="D24" t="n">
-        <v>-410.75</v>
+        <v>262.21</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F24" t="n">
-        <v>927</v>
+        <v>500</v>
       </c>
       <c r="G24" t="n">
-        <v>70.59999999999999</v>
+        <v>262.22</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1628</v>
+      </c>
+      <c r="L24" t="n">
+        <v>115</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.935</t>
+          <t>2026-05-29 09:42:49.892</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779422068851</v>
+        <v>1780022568462</v>
       </c>
       <c r="C25" t="n">
-        <v>85697</v>
+        <v>81383</v>
       </c>
       <c r="D25" t="n">
-        <v>-156.21</v>
+        <v>29.1</v>
       </c>
       <c r="E25" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F25" t="n">
-        <v>927</v>
+        <v>500</v>
       </c>
       <c r="G25" t="n">
-        <v>70.59999999999999</v>
+        <v>262.22</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L25" t="n">
+        <v>106</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.483</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:26.936</t>
+          <t>2026-05-29 09:42:49.913</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779422069053</v>
+        <v>1780022568662</v>
       </c>
       <c r="C26" t="n">
-        <v>86211</v>
+        <v>81302</v>
       </c>
       <c r="D26" t="n">
-        <v>365.6</v>
+        <v>-53.36</v>
       </c>
       <c r="E26" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F26" t="n">
-        <v>927</v>
+        <v>500</v>
       </c>
       <c r="G26" t="n">
-        <v>70.59999999999999</v>
+        <v>262.22</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L26" t="n">
+        <v>105</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:27.360</t>
+          <t>2026-05-29 09:42:49.947</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779422069254</v>
+        <v>1780022568862</v>
       </c>
       <c r="C27" t="n">
-        <v>86290</v>
+        <v>81554</v>
       </c>
       <c r="D27" t="n">
-        <v>426.32</v>
+        <v>201.31</v>
       </c>
       <c r="E27" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F27" t="n">
-        <v>765</v>
+        <v>500</v>
       </c>
       <c r="G27" t="n">
-        <v>71.29000000000001</v>
+        <v>262.22</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L27" t="n">
+        <v>107</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.643</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:27.361</t>
+          <t>2026-05-29 09:42:50.469</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779422069456</v>
+        <v>1780022569081</v>
       </c>
       <c r="C28" t="n">
-        <v>85494</v>
+        <v>81734</v>
       </c>
       <c r="D28" t="n">
-        <v>-391</v>
+        <v>371.25</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F28" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G28" t="n">
-        <v>71.29000000000001</v>
+        <v>262.22</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1387</v>
+      </c>
+      <c r="L28" t="n">
+        <v>106</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:27.737</t>
+          <t>2026-05-29 09:42:50.470</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779422069657</v>
+        <v>1780022569281</v>
       </c>
       <c r="C29" t="n">
-        <v>85721</v>
+        <v>81694</v>
       </c>
       <c r="D29" t="n">
-        <v>-144.45</v>
+        <v>312.68</v>
       </c>
       <c r="E29" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F29" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G29" t="n">
-        <v>71.29000000000001</v>
+        <v>262.22</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L29" t="n">
+        <v>123</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:27.738</t>
+          <t>2026-05-29 09:42:51.826</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779422069858</v>
+        <v>1780022569481</v>
       </c>
       <c r="C30" t="n">
-        <v>85999</v>
+        <v>82359</v>
       </c>
       <c r="D30" t="n">
-        <v>140.77</v>
+        <v>962.05</v>
       </c>
       <c r="E30" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F30" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G30" t="n">
-        <v>71.29000000000001</v>
+        <v>262.22</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2344</v>
+      </c>
+      <c r="L30" t="n">
+        <v>124</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.175</t>
+          <t>2026-05-29 09:42:51.827</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779422070060</v>
+        <v>1780022569681</v>
       </c>
       <c r="C31" t="n">
-        <v>86257</v>
+        <v>81211</v>
       </c>
       <c r="D31" t="n">
-        <v>391.74</v>
+        <v>-234.05</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F31" t="n">
-        <v>866</v>
+        <v>3298</v>
       </c>
       <c r="G31" t="n">
-        <v>74.72</v>
+        <v>262.22</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2145</v>
+      </c>
+      <c r="L31" t="n">
+        <v>128</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.176</t>
+          <t>2026-05-29 09:42:51.828</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779422070261</v>
+        <v>1780022569881</v>
       </c>
       <c r="C32" t="n">
-        <v>85505</v>
+        <v>81401</v>
       </c>
       <c r="D32" t="n">
-        <v>-379.85</v>
+        <v>-32.35</v>
       </c>
       <c r="E32" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F32" t="n">
-        <v>866</v>
+        <v>3298</v>
       </c>
       <c r="G32" t="n">
-        <v>74.72</v>
+        <v>262.22</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1946</v>
+      </c>
+      <c r="L32" t="n">
+        <v>118</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.576</t>
+          <t>2026-05-29 09:42:51.829</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779422070463</v>
+        <v>1780022570081</v>
       </c>
       <c r="C33" t="n">
-        <v>85721</v>
+        <v>81648</v>
       </c>
       <c r="D33" t="n">
-        <v>-144.86</v>
+        <v>216.27</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>866</v>
+        <v>3298</v>
       </c>
       <c r="G33" t="n">
-        <v>74.72</v>
+        <v>262.22</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1747</v>
+      </c>
+      <c r="L33" t="n">
+        <v>118</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.905</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.577</t>
+          <t>2026-05-29 09:42:51.830</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779422070664</v>
+        <v>1780022570282</v>
       </c>
       <c r="C34" t="n">
-        <v>85947</v>
+        <v>81602</v>
       </c>
       <c r="D34" t="n">
-        <v>88.38</v>
+        <v>159.45</v>
       </c>
       <c r="E34" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>866</v>
+        <v>3298</v>
       </c>
       <c r="G34" t="n">
-        <v>74.72</v>
+        <v>262.22</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1547</v>
+      </c>
+      <c r="L34" t="n">
+        <v>107</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.983</t>
+          <t>2026-05-29 09:42:51.831</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779422070865</v>
+        <v>1780022570500</v>
       </c>
       <c r="C35" t="n">
-        <v>86221</v>
+        <v>81585</v>
       </c>
       <c r="D35" t="n">
-        <v>357.97</v>
+        <v>134.48</v>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F35" t="n">
-        <v>806</v>
+        <v>1319</v>
       </c>
       <c r="G35" t="n">
-        <v>68.73</v>
+        <v>312.17</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1331</v>
+      </c>
+      <c r="L35" t="n">
+        <v>117</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.879</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:28.983</t>
+          <t>2026-05-29 09:42:51.833</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779422071067</v>
+        <v>1780022570700</v>
       </c>
       <c r="C36" t="n">
-        <v>85762</v>
+        <v>83190</v>
       </c>
       <c r="D36" t="n">
-        <v>-118.93</v>
+        <v>1732.76</v>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F36" t="n">
-        <v>806</v>
+        <v>1319</v>
       </c>
       <c r="G36" t="n">
-        <v>68.73</v>
+        <v>312.17</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:29.397</t>
+          <t>2026-05-29 09:42:51.833</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779422071268</v>
+        <v>1780022570900</v>
       </c>
       <c r="C37" t="n">
-        <v>85651</v>
+        <v>81778</v>
       </c>
       <c r="D37" t="n">
-        <v>-223.99</v>
+        <v>234.12</v>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F37" t="n">
-        <v>806</v>
+        <v>1319</v>
       </c>
       <c r="G37" t="n">
-        <v>68.73</v>
+        <v>312.17</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>933</v>
+      </c>
+      <c r="L37" t="n">
+        <v>106</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.784</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:29.399</t>
+          <t>2026-05-29 09:42:52.204</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779422071470</v>
+        <v>1780022571100</v>
       </c>
       <c r="C38" t="n">
-        <v>85776</v>
+        <v>81663</v>
       </c>
       <c r="D38" t="n">
-        <v>-87.79000000000001</v>
+        <v>107.41</v>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F38" t="n">
-        <v>806</v>
+        <v>1319</v>
       </c>
       <c r="G38" t="n">
-        <v>68.73</v>
+        <v>312.17</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L38" t="n">
+        <v>109</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.484</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:29.873</t>
+          <t>2026-05-29 09:42:52.289</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779422071671</v>
+        <v>1780022571300</v>
       </c>
       <c r="C39" t="n">
-        <v>86020</v>
+        <v>81605</v>
       </c>
       <c r="D39" t="n">
-        <v>160.6</v>
+        <v>44.04</v>
       </c>
       <c r="E39" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F39" t="n">
-        <v>806</v>
+        <v>1319</v>
       </c>
       <c r="G39" t="n">
-        <v>68.73</v>
+        <v>312.17</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>987</v>
+      </c>
+      <c r="L39" t="n">
+        <v>119</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.315</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:29.888</t>
+          <t>2026-05-29 09:42:52.694</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779422071872</v>
+        <v>1780022571501</v>
       </c>
       <c r="C40" t="n">
-        <v>85964</v>
+        <v>81920</v>
       </c>
       <c r="D40" t="n">
-        <v>96.56999999999999</v>
+        <v>356.84</v>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F40" t="n">
-        <v>926</v>
+        <v>1319</v>
       </c>
       <c r="G40" t="n">
-        <v>75.48999999999999</v>
+        <v>312.17</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L40" t="n">
+        <v>108</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.736</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:29.889</t>
+          <t>2026-05-29 09:42:53.549</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779422072074</v>
+        <v>1780022571700</v>
       </c>
       <c r="C41" t="n">
-        <v>85441</v>
+        <v>82165</v>
       </c>
       <c r="D41" t="n">
-        <v>-431.26</v>
+        <v>584</v>
       </c>
       <c r="E41" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F41" t="n">
-        <v>926</v>
+        <v>1339</v>
       </c>
       <c r="G41" t="n">
-        <v>75.48999999999999</v>
+        <v>350.81</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1848</v>
+      </c>
+      <c r="L41" t="n">
+        <v>111</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:30.196</t>
+          <t>2026-05-29 09:42:53.551</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779422072275</v>
+        <v>1780022571901</v>
       </c>
       <c r="C42" t="n">
-        <v>85628</v>
+        <v>81884</v>
       </c>
       <c r="D42" t="n">
-        <v>-222.69</v>
+        <v>273.8</v>
       </c>
       <c r="E42" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F42" t="n">
-        <v>926</v>
+        <v>1339</v>
       </c>
       <c r="G42" t="n">
-        <v>75.48999999999999</v>
+        <v>350.81</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="J42" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1649</v>
+      </c>
+      <c r="L42" t="n">
+        <v>161</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.845</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:30.198</t>
+          <t>2026-05-29 09:42:53.553</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779422072477</v>
+        <v>1780022572119</v>
       </c>
       <c r="C43" t="n">
-        <v>85838</v>
+        <v>81769</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.56</v>
+        <v>145.11</v>
       </c>
       <c r="E43" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F43" t="n">
-        <v>926</v>
+        <v>1339</v>
       </c>
       <c r="G43" t="n">
-        <v>75.48999999999999</v>
+        <v>350.81</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1433</v>
+      </c>
+      <c r="L43" t="n">
+        <v>119</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:30.615</t>
+          <t>2026-05-29 09:42:53.984</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779422072678</v>
+        <v>1780022572320</v>
       </c>
       <c r="C44" t="n">
-        <v>85584</v>
+        <v>81921</v>
       </c>
       <c r="D44" t="n">
-        <v>-255.48</v>
+        <v>289.85</v>
       </c>
       <c r="E44" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F44" t="n">
-        <v>846</v>
+        <v>1339</v>
       </c>
       <c r="G44" t="n">
-        <v>74.09999999999999</v>
+        <v>350.81</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1662</v>
+      </c>
+      <c r="L44" t="n">
+        <v>108</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.908</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:30.616</t>
+          <t>2026-05-29 09:42:53.986</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779422072879</v>
+        <v>1780022572519</v>
       </c>
       <c r="C45" t="n">
-        <v>85400</v>
+        <v>81909</v>
       </c>
       <c r="D45" t="n">
-        <v>-426.71</v>
+        <v>263.36</v>
       </c>
       <c r="E45" t="n">
         <v>69</v>
       </c>
       <c r="F45" t="n">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="G45" t="n">
-        <v>74.09999999999999</v>
+        <v>327.63</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L45" t="n">
+        <v>117</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:31.023</t>
+          <t>2026-05-29 09:42:53.994</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779422073081</v>
+        <v>1780022572719</v>
       </c>
       <c r="C46" t="n">
-        <v>85463</v>
+        <v>82002</v>
       </c>
       <c r="D46" t="n">
-        <v>-342.37</v>
+        <v>343.19</v>
       </c>
       <c r="E46" t="n">
         <v>69</v>
       </c>
       <c r="F46" t="n">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="G46" t="n">
-        <v>74.09999999999999</v>
+        <v>327.63</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L46" t="n">
+        <v>120</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.157</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:31.024</t>
+          <t>2026-05-29 09:42:53.996</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779422073282</v>
+        <v>1780022572919</v>
       </c>
       <c r="C47" t="n">
-        <v>85810</v>
+        <v>81744</v>
       </c>
       <c r="D47" t="n">
-        <v>21.75</v>
+        <v>68.03</v>
       </c>
       <c r="E47" t="n">
         <v>69</v>
       </c>
       <c r="F47" t="n">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="G47" t="n">
-        <v>74.09999999999999</v>
+        <v>327.63</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1076</v>
+      </c>
+      <c r="L47" t="n">
+        <v>105</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.489</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:31.740</t>
+          <t>2026-05-29 09:42:54.490</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779422073484</v>
+        <v>1780022573119</v>
       </c>
       <c r="C48" t="n">
-        <v>85164</v>
+        <v>82720</v>
       </c>
       <c r="D48" t="n">
-        <v>-625.34</v>
+        <v>1040.63</v>
       </c>
       <c r="E48" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F48" t="n">
-        <v>786</v>
+        <v>859</v>
       </c>
       <c r="G48" t="n">
-        <v>74.05</v>
+        <v>327.63</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:31.746</t>
+          <t>2026-05-29 09:42:54.547</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779422073685</v>
+        <v>1780022573319</v>
       </c>
       <c r="C49" t="n">
-        <v>85392</v>
+        <v>82876</v>
       </c>
       <c r="D49" t="n">
-        <v>-366.07</v>
+        <v>1144.6</v>
       </c>
       <c r="E49" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F49" t="n">
-        <v>786</v>
+        <v>620</v>
       </c>
       <c r="G49" t="n">
-        <v>74.05</v>
+        <v>335.61</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1227</v>
+      </c>
+      <c r="L49" t="n">
+        <v>112</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:31.773</t>
+          <t>2026-05-29 09:42:54.548</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779422073886</v>
+        <v>1780022573538</v>
       </c>
       <c r="C50" t="n">
-        <v>85604</v>
+        <v>82461</v>
       </c>
       <c r="D50" t="n">
-        <v>-135.77</v>
+        <v>672.37</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F50" t="n">
-        <v>786</v>
+        <v>620</v>
       </c>
       <c r="G50" t="n">
-        <v>74.05</v>
+        <v>335.61</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J50" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1009</v>
+      </c>
+      <c r="L50" t="n">
+        <v>105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.038</t>
+          <t>2026-05-29 09:42:54.874</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779422074088</v>
+        <v>1780022573738</v>
       </c>
       <c r="C51" t="n">
-        <v>85898</v>
+        <v>84596</v>
       </c>
       <c r="D51" t="n">
-        <v>165.02</v>
+        <v>2773.75</v>
       </c>
       <c r="E51" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F51" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="G51" t="n">
-        <v>88.41</v>
+        <v>335.61</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L51" t="n">
+        <v>108</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.039</t>
+          <t>2026-05-29 09:42:54.875</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779422074289</v>
+        <v>1780022573938</v>
       </c>
       <c r="C52" t="n">
-        <v>85200</v>
+        <v>87389</v>
       </c>
       <c r="D52" t="n">
-        <v>-541.23</v>
+        <v>5428.06</v>
       </c>
       <c r="E52" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F52" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="G52" t="n">
-        <v>88.41</v>
+        <v>335.61</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>936</v>
+      </c>
+      <c r="L52" t="n">
+        <v>96</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.482</t>
+          <t>2026-05-29 09:42:54.877</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779422074491</v>
+        <v>1780022574138</v>
       </c>
       <c r="C53" t="n">
-        <v>85428</v>
+        <v>84876</v>
       </c>
       <c r="D53" t="n">
-        <v>-286.17</v>
+        <v>2643.66</v>
       </c>
       <c r="E53" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F53" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="G53" t="n">
-        <v>88.41</v>
+        <v>335.61</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>737</v>
+      </c>
+      <c r="L53" t="n">
+        <v>106</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.483</t>
+          <t>2026-05-29 09:42:55.354</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779422074692</v>
+        <v>1780022574338</v>
       </c>
       <c r="C54" t="n">
-        <v>85655</v>
+        <v>83272</v>
       </c>
       <c r="D54" t="n">
-        <v>-44.86</v>
+        <v>907.48</v>
       </c>
       <c r="E54" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F54" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="G54" t="n">
-        <v>88.41</v>
+        <v>335.61</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L54" t="n">
+        <v>110</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.207</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.881</t>
+          <t>2026-05-29 09:42:55.982</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779422074893</v>
+        <v>1780022574538</v>
       </c>
       <c r="C55" t="n">
-        <v>85432</v>
+        <v>83451</v>
       </c>
       <c r="D55" t="n">
-        <v>-265.62</v>
+        <v>1041.1</v>
       </c>
       <c r="E55" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F55" t="n">
-        <v>766</v>
+        <v>620</v>
       </c>
       <c r="G55" t="n">
-        <v>82.78</v>
+        <v>335.61</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L55" t="n">
+        <v>106</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.188</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:32.883</t>
+          <t>2026-05-29 09:42:55.988</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779422075095</v>
+        <v>1780022574738</v>
       </c>
       <c r="C56" t="n">
-        <v>85207</v>
+        <v>83582</v>
       </c>
       <c r="D56" t="n">
-        <v>-477.34</v>
+        <v>1120.05</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F56" t="n">
-        <v>766</v>
+        <v>620</v>
       </c>
       <c r="G56" t="n">
-        <v>82.78</v>
+        <v>335.61</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L56" t="n">
+        <v>109</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.136</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:33.440</t>
+          <t>2026-05-29 09:42:55.991</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779422075296</v>
+        <v>1780022574938</v>
       </c>
       <c r="C57" t="n">
-        <v>85433</v>
+        <v>83396</v>
       </c>
       <c r="D57" t="n">
-        <v>-227.47</v>
+        <v>878.05</v>
       </c>
       <c r="E57" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F57" t="n">
-        <v>766</v>
+        <v>620</v>
       </c>
       <c r="G57" t="n">
-        <v>82.78</v>
+        <v>335.61</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L57" t="n">
+        <v>106</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:33.441</t>
+          <t>2026-05-29 09:42:56.229</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779422075498</v>
+        <v>1780022575157</v>
       </c>
       <c r="C58" t="n">
-        <v>85639</v>
+        <v>83853</v>
       </c>
       <c r="D58" t="n">
-        <v>-10.1</v>
+        <v>1291.14</v>
       </c>
       <c r="E58" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F58" t="n">
-        <v>704</v>
+        <v>620</v>
       </c>
       <c r="G58" t="n">
-        <v>87.23</v>
+        <v>335.61</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L58" t="n">
+        <v>108</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.193</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:33.725</t>
+          <t>2026-05-29 09:42:56.256</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779422075699</v>
+        <v>1780022575357</v>
       </c>
       <c r="C59" t="n">
-        <v>85010</v>
+        <v>83412</v>
       </c>
       <c r="D59" t="n">
-        <v>-638.59</v>
+        <v>785.59</v>
       </c>
       <c r="E59" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F59" t="n">
-        <v>704</v>
+        <v>620</v>
       </c>
       <c r="G59" t="n">
-        <v>87.23</v>
+        <v>335.61</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>898</v>
+      </c>
+      <c r="L59" t="n">
+        <v>106</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.508</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:33.726</t>
+          <t>2026-05-29 09:42:57.289</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779422075900</v>
+        <v>1780022575557</v>
       </c>
       <c r="C60" t="n">
-        <v>85276</v>
+        <v>83497</v>
       </c>
       <c r="D60" t="n">
-        <v>-340.66</v>
+        <v>831.3099999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F60" t="n">
-        <v>704</v>
+        <v>620</v>
       </c>
       <c r="G60" t="n">
-        <v>87.23</v>
+        <v>335.61</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1731</v>
+      </c>
+      <c r="L60" t="n">
+        <v>114</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.169</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.149</t>
+          <t>2026-05-29 09:42:57.291</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779422076102</v>
+        <v>1780022575757</v>
       </c>
       <c r="C61" t="n">
-        <v>85648</v>
+        <v>83574</v>
       </c>
       <c r="D61" t="n">
-        <v>48.37</v>
+        <v>866.74</v>
       </c>
       <c r="E61" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F61" t="n">
-        <v>704</v>
+        <v>620</v>
       </c>
       <c r="G61" t="n">
-        <v>87.23</v>
+        <v>335.61</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1533</v>
+      </c>
+      <c r="L61" t="n">
+        <v>105</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.149</t>
+          <t>2026-05-29 09:42:57.597</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779422076303</v>
+        <v>1780022575957</v>
       </c>
       <c r="C62" t="n">
-        <v>85382</v>
+        <v>84132</v>
       </c>
       <c r="D62" t="n">
-        <v>-220.05</v>
+        <v>1381.4</v>
       </c>
       <c r="E62" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F62" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G62" t="n">
-        <v>86.06</v>
+        <v>335.61</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1639</v>
+      </c>
+      <c r="L62" t="n">
+        <v>117</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.499</t>
+          <t>2026-05-29 09:42:57.598</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779422076505</v>
+        <v>1780022576157</v>
       </c>
       <c r="C63" t="n">
-        <v>85331</v>
+        <v>84753</v>
       </c>
       <c r="D63" t="n">
-        <v>-260.05</v>
+        <v>1933.33</v>
       </c>
       <c r="E63" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F63" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G63" t="n">
-        <v>86.06</v>
+        <v>335.61</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1440</v>
+      </c>
+      <c r="L63" t="n">
+        <v>111</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.182</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.499</t>
+          <t>2026-05-29 09:42:57.600</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779422076706</v>
+        <v>1780022576357</v>
       </c>
       <c r="C64" t="n">
-        <v>85684</v>
+        <v>82795</v>
       </c>
       <c r="D64" t="n">
-        <v>105.96</v>
+        <v>-121.33</v>
       </c>
       <c r="E64" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F64" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G64" t="n">
-        <v>86.06</v>
+        <v>335.61</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L64" t="n">
+        <v>111</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.149</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.984</t>
+          <t>2026-05-29 09:42:57.601</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779422076907</v>
+        <v>1780022576576</v>
       </c>
       <c r="C65" t="n">
-        <v>86097</v>
+        <v>82352</v>
       </c>
       <c r="D65" t="n">
-        <v>513.66</v>
+        <v>-558.27</v>
       </c>
       <c r="E65" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F65" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G65" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L65" t="n">
+        <v>109</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.253</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:34.984</t>
+          <t>2026-05-29 09:42:57.975</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779422077109</v>
+        <v>1780022576776</v>
       </c>
       <c r="C66" t="n">
-        <v>85645</v>
+        <v>83475</v>
       </c>
       <c r="D66" t="n">
-        <v>35.98</v>
+        <v>592.65</v>
       </c>
       <c r="E66" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F66" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G66" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L66" t="n">
+        <v>110</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.073</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:35.326</t>
+          <t>2026-05-29 09:42:57.991</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779422077310</v>
+        <v>1780022576976</v>
       </c>
       <c r="C67" t="n">
-        <v>86015</v>
+        <v>84525</v>
       </c>
       <c r="D67" t="n">
-        <v>404.18</v>
+        <v>1613.02</v>
       </c>
       <c r="E67" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F67" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G67" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L67" t="n">
+        <v>114</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.212</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:35.326</t>
+          <t>2026-05-29 09:42:58.007</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779422077512</v>
+        <v>1780022577176</v>
       </c>
       <c r="C68" t="n">
-        <v>86337</v>
+        <v>84294</v>
       </c>
       <c r="D68" t="n">
-        <v>705.97</v>
+        <v>1301.36</v>
       </c>
       <c r="E68" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F68" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G68" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>829</v>
+      </c>
+      <c r="L68" t="n">
+        <v>117</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.201</t>
+          <t>2026-05-29 09:42:59.549</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779422077713</v>
+        <v>1780022577376</v>
       </c>
       <c r="C69" t="n">
-        <v>86536</v>
+        <v>83588</v>
       </c>
       <c r="D69" t="n">
-        <v>869.67</v>
+        <v>530.3</v>
       </c>
       <c r="E69" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F69" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G69" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2172</v>
+      </c>
+      <c r="L69" t="n">
+        <v>115</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.215</t>
+          <t>2026-05-29 09:42:59.557</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779422077914</v>
+        <v>1780022577576</v>
       </c>
       <c r="C70" t="n">
-        <v>85878</v>
+        <v>83427</v>
       </c>
       <c r="D70" t="n">
-        <v>168.19</v>
+        <v>342.78</v>
       </c>
       <c r="E70" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F70" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G70" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1980</v>
+      </c>
+      <c r="L70" t="n">
+        <v>111</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.215</t>
+          <t>2026-05-29 09:42:59.597</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779422078116</v>
+        <v>1780022577776</v>
       </c>
       <c r="C71" t="n">
-        <v>86215</v>
+        <v>82880</v>
       </c>
       <c r="D71" t="n">
-        <v>496.78</v>
+        <v>-221.36</v>
       </c>
       <c r="E71" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F71" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G71" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1819</v>
+      </c>
+      <c r="L71" t="n">
+        <v>117</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.023</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.216</t>
+          <t>2026-05-29 09:42:59.599</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779422078317</v>
+        <v>1780022577976</v>
       </c>
       <c r="C72" t="n">
-        <v>86743</v>
+        <v>82476</v>
       </c>
       <c r="D72" t="n">
-        <v>999.9400000000001</v>
+        <v>-614.29</v>
       </c>
       <c r="E72" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F72" t="n">
-        <v>644</v>
+        <v>2798</v>
       </c>
       <c r="G72" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1622</v>
+      </c>
+      <c r="L72" t="n">
+        <v>108</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.589</t>
+          <t>2026-05-29 09:42:59.616</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779422078519</v>
+        <v>1780022578195</v>
       </c>
       <c r="C73" t="n">
-        <v>86936</v>
+        <v>82509</v>
       </c>
       <c r="D73" t="n">
-        <v>1142.94</v>
+        <v>-550.58</v>
       </c>
       <c r="E73" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F73" t="n">
-        <v>1571</v>
+        <v>2798</v>
       </c>
       <c r="G73" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1420</v>
+      </c>
+      <c r="L73" t="n">
+        <v>118</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.848</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.589</t>
+          <t>2026-05-29 09:42:59.813</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779422078720</v>
+        <v>1780022578395</v>
       </c>
       <c r="C74" t="n">
-        <v>86350</v>
+        <v>82509</v>
       </c>
       <c r="D74" t="n">
-        <v>499.79</v>
+        <v>-523.05</v>
       </c>
       <c r="E74" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F74" t="n">
-        <v>1571</v>
+        <v>2798</v>
       </c>
       <c r="G74" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L74" t="n">
+        <v>107</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.455</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.970</t>
+          <t>2026-05-29 09:42:59.817</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779422078922</v>
+        <v>1780022578595</v>
       </c>
       <c r="C75" t="n">
-        <v>86949</v>
+        <v>82562</v>
       </c>
       <c r="D75" t="n">
-        <v>1073.8</v>
+        <v>-443.89</v>
       </c>
       <c r="E75" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F75" t="n">
-        <v>1571</v>
+        <v>2798</v>
       </c>
       <c r="G75" t="n">
-        <v>96.22</v>
+        <v>335.61</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L75" t="n">
+        <v>116</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.469</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:36.972</t>
+          <t>2026-05-29 09:42:59.818</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779422079123</v>
+        <v>1780022578795</v>
       </c>
       <c r="C76" t="n">
-        <v>87445</v>
+        <v>82659</v>
       </c>
       <c r="D76" t="n">
-        <v>1516.11</v>
+        <v>-324.7</v>
       </c>
       <c r="E76" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F76" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G76" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L76" t="n">
+        <v>111</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.485</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:37.776</t>
+          <t>2026-05-29 09:43:00.187</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779422079324</v>
+        <v>1780022578995</v>
       </c>
       <c r="C77" t="n">
-        <v>87169</v>
+        <v>82483</v>
       </c>
       <c r="D77" t="n">
-        <v>1164.31</v>
+        <v>-484.46</v>
       </c>
       <c r="E77" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F77" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G77" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L77" t="n">
+        <v>116</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.763</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:37.776</t>
+          <t>2026-05-29 09:43:00.188</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779422079526</v>
+        <v>1780022579195</v>
       </c>
       <c r="C78" t="n">
-        <v>87340</v>
+        <v>82359</v>
       </c>
       <c r="D78" t="n">
-        <v>1277.09</v>
+        <v>-584.24</v>
       </c>
       <c r="E78" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F78" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G78" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>992</v>
+      </c>
+      <c r="L78" t="n">
+        <v>107</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.555</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:37.777</t>
+          <t>2026-05-29 09:43:01.008</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779422079727</v>
+        <v>1780022579395</v>
       </c>
       <c r="C79" t="n">
-        <v>86923</v>
+        <v>82365</v>
       </c>
       <c r="D79" t="n">
-        <v>796.24</v>
+        <v>-549.03</v>
       </c>
       <c r="E79" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F79" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G79" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1612</v>
+      </c>
+      <c r="L79" t="n">
+        <v>119</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.929</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:37.777</t>
+          <t>2026-05-29 09:43:01.010</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779422079929</v>
+        <v>1780022579595</v>
       </c>
       <c r="C80" t="n">
-        <v>87072</v>
+        <v>82375</v>
       </c>
       <c r="D80" t="n">
-        <v>905.4299999999999</v>
+        <v>-511.58</v>
       </c>
       <c r="E80" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F80" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G80" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1414</v>
+      </c>
+      <c r="L80" t="n">
+        <v>109</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:38.185</t>
+          <t>2026-05-29 09:43:01.011</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779422080130</v>
+        <v>1780022579814</v>
       </c>
       <c r="C81" t="n">
-        <v>87611</v>
+        <v>82340</v>
       </c>
       <c r="D81" t="n">
-        <v>1399.16</v>
+        <v>-521</v>
       </c>
       <c r="E81" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F81" t="n">
-        <v>665</v>
+        <v>2798</v>
       </c>
       <c r="G81" t="n">
-        <v>94.28</v>
+        <v>335.61</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1196</v>
+      </c>
+      <c r="L81" t="n">
+        <v>112</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:38.186</t>
+          <t>2026-05-29 09:43:01.012</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779422080331</v>
+        <v>1780022580014</v>
       </c>
       <c r="C82" t="n">
-        <v>87226</v>
+        <v>82513</v>
       </c>
       <c r="D82" t="n">
-        <v>944.2</v>
+        <v>-321.95</v>
       </c>
       <c r="E82" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F82" t="n">
-        <v>1269</v>
+        <v>4057</v>
       </c>
       <c r="G82" t="n">
-        <v>190.72</v>
+        <v>335.61</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>997</v>
+      </c>
+      <c r="L82" t="n">
+        <v>109</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.891</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:38.593</t>
+          <t>2026-05-29 09:43:02.412</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779422080533</v>
+        <v>1780022580214</v>
       </c>
       <c r="C83" t="n">
-        <v>87281</v>
+        <v>82612</v>
       </c>
       <c r="D83" t="n">
-        <v>951.99</v>
+        <v>-206.85</v>
       </c>
       <c r="E83" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F83" t="n">
-        <v>1269</v>
+        <v>4057</v>
       </c>
       <c r="G83" t="n">
-        <v>190.72</v>
+        <v>335.61</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2197</v>
+      </c>
+      <c r="L83" t="n">
+        <v>108</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.072</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:38.594</t>
+          <t>2026-05-29 09:43:02.424</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779422080734</v>
+        <v>1780022580414</v>
       </c>
       <c r="C84" t="n">
-        <v>86519</v>
+        <v>83391</v>
       </c>
       <c r="D84" t="n">
-        <v>142.39</v>
+        <v>582.49</v>
       </c>
       <c r="E84" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F84" t="n">
-        <v>1269</v>
+        <v>4057</v>
       </c>
       <c r="G84" t="n">
-        <v>190.72</v>
+        <v>335.61</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J84" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L84" t="n">
+        <v>117</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.996</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:39.209</t>
+          <t>2026-05-29 09:43:02.425</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779422080935</v>
+        <v>1780022580614</v>
       </c>
       <c r="C85" t="n">
-        <v>86717</v>
+        <v>82559</v>
       </c>
       <c r="D85" t="n">
-        <v>333.27</v>
+        <v>-278.63</v>
       </c>
       <c r="E85" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F85" t="n">
-        <v>1269</v>
+        <v>4057</v>
       </c>
       <c r="G85" t="n">
-        <v>190.72</v>
+        <v>335.61</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1810</v>
+      </c>
+      <c r="L85" t="n">
+        <v>118</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:39.210</t>
+          <t>2026-05-29 09:43:02.458</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779422081137</v>
+        <v>1780022580814</v>
       </c>
       <c r="C86" t="n">
-        <v>86978</v>
+        <v>82044</v>
       </c>
       <c r="D86" t="n">
-        <v>577.61</v>
+        <v>-779.7</v>
       </c>
       <c r="E86" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F86" t="n">
-        <v>1269</v>
+        <v>4057</v>
       </c>
       <c r="G86" t="n">
-        <v>190.72</v>
+        <v>335.61</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1643</v>
+      </c>
+      <c r="L86" t="n">
+        <v>108</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.797</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:39.211</t>
+          <t>2026-05-29 09:43:02.492</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779422081338</v>
+        <v>1780022581014</v>
       </c>
       <c r="C87" t="n">
-        <v>86983</v>
+        <v>82215</v>
       </c>
       <c r="D87" t="n">
-        <v>553.73</v>
+        <v>-569.72</v>
       </c>
       <c r="E87" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F87" t="n">
-        <v>1007</v>
+        <v>4057</v>
       </c>
       <c r="G87" t="n">
-        <v>198.54</v>
+        <v>335.61</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1477</v>
+      </c>
+      <c r="L87" t="n">
+        <v>108</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.451</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:39.644</t>
+          <t>2026-05-29 09:43:02.494</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779422081540</v>
+        <v>1780022581214</v>
       </c>
       <c r="C88" t="n">
-        <v>86756</v>
+        <v>82209</v>
       </c>
       <c r="D88" t="n">
-        <v>299.04</v>
+        <v>-547.23</v>
       </c>
       <c r="E88" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F88" t="n">
-        <v>1007</v>
+        <v>4057</v>
       </c>
       <c r="G88" t="n">
-        <v>198.54</v>
+        <v>335.61</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1279</v>
+      </c>
+      <c r="L88" t="n">
+        <v>108</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:39.647</t>
+          <t>2026-05-29 09:43:02.637</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779422081741</v>
+        <v>1780022581433</v>
       </c>
       <c r="C89" t="n">
-        <v>87001</v>
+        <v>82770</v>
       </c>
       <c r="D89" t="n">
-        <v>529.09</v>
+        <v>41.13</v>
       </c>
       <c r="E89" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F89" t="n">
-        <v>1007</v>
+        <v>4057</v>
       </c>
       <c r="G89" t="n">
-        <v>198.54</v>
+        <v>335.61</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1204</v>
+      </c>
+      <c r="L89" t="n">
+        <v>110</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.826</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:40.036</t>
+          <t>2026-05-29 09:43:02.785</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779422081943</v>
+        <v>1780022581633</v>
       </c>
       <c r="C90" t="n">
-        <v>87186</v>
+        <v>82906</v>
       </c>
       <c r="D90" t="n">
-        <v>687.63</v>
+        <v>175.07</v>
       </c>
       <c r="E90" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F90" t="n">
-        <v>544</v>
+        <v>4057</v>
       </c>
       <c r="G90" t="n">
-        <v>213.44</v>
+        <v>335.61</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J90" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L90" t="n">
+        <v>117</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.144</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:40.066</t>
+          <t>2026-05-29 09:43:02.788</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779422082144</v>
+        <v>1780022581833</v>
       </c>
       <c r="C91" t="n">
-        <v>86716</v>
+        <v>82355</v>
       </c>
       <c r="D91" t="n">
-        <v>183.25</v>
+        <v>-384.68</v>
       </c>
       <c r="E91" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F91" t="n">
-        <v>544</v>
+        <v>4057</v>
       </c>
       <c r="G91" t="n">
-        <v>213.44</v>
+        <v>335.61</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J91" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K91" t="n">
+        <v>954</v>
+      </c>
+      <c r="L91" t="n">
+        <v>113</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.754</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:40.487</t>
+          <t>2026-05-29 09:43:04.777</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779422082345</v>
+        <v>1780022582033</v>
       </c>
       <c r="C92" t="n">
-        <v>86849</v>
+        <v>82275</v>
       </c>
       <c r="D92" t="n">
-        <v>307.09</v>
+        <v>-445.45</v>
       </c>
       <c r="E92" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F92" t="n">
-        <v>544</v>
+        <v>4057</v>
       </c>
       <c r="G92" t="n">
-        <v>213.44</v>
+        <v>335.61</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2743</v>
+      </c>
+      <c r="L92" t="n">
+        <v>115</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.463</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:40.488</t>
+          <t>2026-05-29 09:43:04.777</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779422082547</v>
+        <v>1780022582233</v>
       </c>
       <c r="C93" t="n">
-        <v>87104</v>
+        <v>82244</v>
       </c>
       <c r="D93" t="n">
-        <v>546.73</v>
+        <v>-454.17</v>
       </c>
       <c r="E93" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F93" t="n">
-        <v>544</v>
+        <v>4057</v>
       </c>
       <c r="G93" t="n">
-        <v>213.44</v>
+        <v>335.61</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2544</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.444</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.256</t>
+          <t>2026-05-29 09:43:04.778</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779422082748</v>
+        <v>1780022582433</v>
       </c>
       <c r="C94" t="n">
-        <v>86633</v>
+        <v>82616</v>
       </c>
       <c r="D94" t="n">
-        <v>48.4</v>
+        <v>-59.46</v>
       </c>
       <c r="E94" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F94" t="n">
-        <v>745</v>
+        <v>4057</v>
       </c>
       <c r="G94" t="n">
-        <v>213.52</v>
+        <v>335.61</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2345</v>
+      </c>
+      <c r="L94" t="n">
+        <v>122</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.452</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.281</t>
+          <t>2026-05-29 09:43:04.779</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779422082950</v>
+        <v>1780022582633</v>
       </c>
       <c r="C95" t="n">
-        <v>87107</v>
+        <v>82611</v>
       </c>
       <c r="D95" t="n">
-        <v>519.98</v>
+        <v>-61.49</v>
       </c>
       <c r="E95" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F95" t="n">
-        <v>745</v>
+        <v>2519</v>
       </c>
       <c r="G95" t="n">
-        <v>213.52</v>
+        <v>335.61</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2145</v>
+      </c>
+      <c r="L95" t="n">
+        <v>107</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.448</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.282</t>
+          <t>2026-05-29 09:43:04.779</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779422083151</v>
+        <v>1780022582852</v>
       </c>
       <c r="C96" t="n">
-        <v>87406</v>
+        <v>81917</v>
       </c>
       <c r="D96" t="n">
-        <v>792.98</v>
+        <v>-752.42</v>
       </c>
       <c r="E96" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="F96" t="n">
-        <v>483</v>
+        <v>2519</v>
       </c>
       <c r="G96" t="n">
-        <v>230.27</v>
+        <v>335.61</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1927</v>
+      </c>
+      <c r="L96" t="n">
+        <v>110</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.515</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.282</t>
+          <t>2026-05-29 09:43:04.780</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779422083352</v>
+        <v>1780022583052</v>
       </c>
       <c r="C97" t="n">
-        <v>86964</v>
+        <v>81931</v>
       </c>
       <c r="D97" t="n">
-        <v>311.33</v>
+        <v>-700.8</v>
       </c>
       <c r="E97" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="F97" t="n">
-        <v>483</v>
+        <v>2519</v>
       </c>
       <c r="G97" t="n">
-        <v>230.27</v>
+        <v>335.61</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1728</v>
+      </c>
+      <c r="L97" t="n">
+        <v>112</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.473</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.763</t>
+          <t>2026-05-29 09:43:04.987</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779422083554</v>
+        <v>1780022583252</v>
       </c>
       <c r="C98" t="n">
-        <v>87080</v>
+        <v>82112</v>
       </c>
       <c r="D98" t="n">
-        <v>411.76</v>
+        <v>-484.76</v>
       </c>
       <c r="E98" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="F98" t="n">
-        <v>483</v>
+        <v>2519</v>
       </c>
       <c r="G98" t="n">
-        <v>230.27</v>
+        <v>335.61</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1734</v>
+      </c>
+      <c r="L98" t="n">
+        <v>107</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:41.764</t>
+          <t>2026-05-29 09:43:04.989</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779422083755</v>
+        <v>1780022583452</v>
       </c>
       <c r="C99" t="n">
-        <v>87298</v>
+        <v>82097</v>
       </c>
       <c r="D99" t="n">
-        <v>609.17</v>
+        <v>-475.52</v>
       </c>
       <c r="E99" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="F99" t="n">
-        <v>483</v>
+        <v>2519</v>
       </c>
       <c r="G99" t="n">
-        <v>230.27</v>
+        <v>335.61</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J99" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1536</v>
+      </c>
+      <c r="L99" t="n">
+        <v>117</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.258</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.077</t>
+          <t>2026-05-29 09:43:05.080</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779422083957</v>
+        <v>1780022583652</v>
       </c>
       <c r="C100" t="n">
-        <v>87499</v>
+        <v>82540</v>
       </c>
       <c r="D100" t="n">
-        <v>779.72</v>
+        <v>-8.74</v>
       </c>
       <c r="E100" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F100" t="n">
-        <v>786</v>
+        <v>1019</v>
       </c>
       <c r="G100" t="n">
-        <v>230.52</v>
+        <v>335.86</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J100" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L100" t="n">
+        <v>116</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.905</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.078</t>
+          <t>2026-05-29 09:43:05.639</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779422084158</v>
+        <v>1780022583852</v>
       </c>
       <c r="C101" t="n">
-        <v>86842</v>
+        <v>82551</v>
       </c>
       <c r="D101" t="n">
-        <v>83.73</v>
+        <v>2.69</v>
       </c>
       <c r="E101" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F101" t="n">
-        <v>786</v>
+        <v>1019</v>
       </c>
       <c r="G101" t="n">
-        <v>230.52</v>
+        <v>335.86</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L101" t="n">
+        <v>121</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.014</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.078</t>
+          <t>2026-05-29 09:43:05.640</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779422084359</v>
+        <v>1780022584052</v>
       </c>
       <c r="C102" t="n">
-        <v>87046</v>
+        <v>82670</v>
       </c>
       <c r="D102" t="n">
-        <v>283.54</v>
+        <v>121.56</v>
       </c>
       <c r="E102" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F102" t="n">
-        <v>786</v>
+        <v>1019</v>
       </c>
       <c r="G102" t="n">
-        <v>230.52</v>
+        <v>335.86</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1587</v>
+      </c>
+      <c r="L102" t="n">
+        <v>107</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.528</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.524</t>
+          <t>2026-05-29 09:43:05.643</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779422084561</v>
+        <v>1780022584252</v>
       </c>
       <c r="C103" t="n">
-        <v>87280</v>
+        <v>81804</v>
       </c>
       <c r="D103" t="n">
-        <v>503.37</v>
+        <v>-750.52</v>
       </c>
       <c r="E103" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F103" t="n">
-        <v>786</v>
+        <v>1019</v>
       </c>
       <c r="G103" t="n">
-        <v>230.52</v>
+        <v>335.86</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1389</v>
+      </c>
+      <c r="L103" t="n">
+        <v>110</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.766</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.525</t>
+          <t>2026-05-29 09:43:05.644</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779422084762</v>
+        <v>1780022584452</v>
       </c>
       <c r="C104" t="n">
-        <v>87142</v>
+        <v>83349</v>
       </c>
       <c r="D104" t="n">
-        <v>340.2</v>
+        <v>832.01</v>
       </c>
       <c r="E104" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="F104" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G104" t="n">
-        <v>229.94</v>
+        <v>335.86</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L104" t="n">
+        <v>103</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.872</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.995</t>
+          <t>2026-05-29 09:43:06.403</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779422084964</v>
+        <v>1780022584671</v>
       </c>
       <c r="C105" t="n">
-        <v>86674</v>
+        <v>83389</v>
       </c>
       <c r="D105" t="n">
-        <v>-144.81</v>
+        <v>830.41</v>
       </c>
       <c r="E105" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F105" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G105" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1731</v>
+      </c>
+      <c r="L105" t="n">
+        <v>113</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.256</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:42.996</t>
+          <t>2026-05-29 09:43:06.404</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779422085165</v>
+        <v>1780022584871</v>
       </c>
       <c r="C106" t="n">
-        <v>86813</v>
+        <v>82359</v>
       </c>
       <c r="D106" t="n">
-        <v>1.43</v>
+        <v>-241.11</v>
       </c>
       <c r="E106" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F106" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G106" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1532</v>
+      </c>
+      <c r="L106" t="n">
+        <v>110</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:43.360</t>
+          <t>2026-05-29 09:43:06.406</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779422085366</v>
+        <v>1780022585071</v>
       </c>
       <c r="C107" t="n">
-        <v>86808</v>
+        <v>81940</v>
       </c>
       <c r="D107" t="n">
-        <v>-3.64</v>
+        <v>-648.0599999999999</v>
       </c>
       <c r="E107" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F107" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G107" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1333</v>
+      </c>
+      <c r="L107" t="n">
+        <v>107</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:43.364</t>
+          <t>2026-05-29 09:43:06.407</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779422085568</v>
+        <v>1780022585271</v>
       </c>
       <c r="C108" t="n">
-        <v>86247</v>
+        <v>81819</v>
       </c>
       <c r="D108" t="n">
-        <v>-564.46</v>
+        <v>-736.65</v>
       </c>
       <c r="E108" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F108" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G108" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L108" t="n">
+        <v>106</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:43.712</t>
+          <t>2026-05-29 09:43:08.046</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779422085769</v>
+        <v>1780022585471</v>
       </c>
       <c r="C109" t="n">
-        <v>86446</v>
+        <v>82454</v>
       </c>
       <c r="D109" t="n">
-        <v>-337.24</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F109" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G109" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2574</v>
+      </c>
+      <c r="L109" t="n">
+        <v>110</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.144</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:43.713</t>
+          <t>2026-05-29 09:43:08.048</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779422085971</v>
+        <v>1780022585671</v>
       </c>
       <c r="C110" t="n">
-        <v>86606</v>
+        <v>82548</v>
       </c>
       <c r="D110" t="n">
-        <v>-160.38</v>
+        <v>32.42</v>
       </c>
       <c r="E110" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F110" t="n">
-        <v>765</v>
+        <v>1019</v>
       </c>
       <c r="G110" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2376</v>
+      </c>
+      <c r="L110" t="n">
+        <v>117</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.078</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:44.202</t>
+          <t>2026-05-29 09:43:08.050</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779422086172</v>
+        <v>1780022585871</v>
       </c>
       <c r="C111" t="n">
-        <v>86757</v>
+        <v>82593</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.36</v>
+        <v>75.8</v>
       </c>
       <c r="E111" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F111" t="n">
-        <v>1551</v>
+        <v>1019</v>
       </c>
       <c r="G111" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2179</v>
+      </c>
+      <c r="L111" t="n">
+        <v>119</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:44.246</t>
+          <t>2026-05-29 09:43:08.053</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779422086373</v>
+        <v>1780022586071</v>
       </c>
       <c r="C112" t="n">
-        <v>86220</v>
+        <v>82308</v>
       </c>
       <c r="D112" t="n">
-        <v>-538.29</v>
+        <v>-212.99</v>
       </c>
       <c r="E112" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F112" t="n">
-        <v>1551</v>
+        <v>1019</v>
       </c>
       <c r="G112" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1980</v>
+      </c>
+      <c r="L112" t="n">
+        <v>109</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.611</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:44.540</t>
+          <t>2026-05-29 09:43:08.054</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779422086575</v>
+        <v>1780022586290</v>
       </c>
       <c r="C113" t="n">
-        <v>86441</v>
+        <v>82624</v>
       </c>
       <c r="D113" t="n">
-        <v>-290.37</v>
+        <v>113.66</v>
       </c>
       <c r="E113" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F113" t="n">
-        <v>1551</v>
+        <v>1019</v>
       </c>
       <c r="G113" t="n">
-        <v>229.94</v>
+        <v>336.63</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1763</v>
+      </c>
+      <c r="L113" t="n">
+        <v>107</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:44.560</t>
+          <t>2026-05-29 09:43:08.057</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779422086776</v>
+        <v>1780022586490</v>
       </c>
       <c r="C114" t="n">
-        <v>86706</v>
+        <v>82770</v>
       </c>
       <c r="D114" t="n">
-        <v>-10.86</v>
+        <v>253.98</v>
       </c>
       <c r="E114" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F114" t="n">
-        <v>624</v>
+        <v>1839</v>
       </c>
       <c r="G114" t="n">
-        <v>232.12</v>
+        <v>336.63</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1566</v>
+      </c>
+      <c r="L114" t="n">
+        <v>107</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.31</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.061</t>
+          <t>2026-05-29 09:43:08.571</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779422086978</v>
+        <v>1780022586690</v>
       </c>
       <c r="C115" t="n">
-        <v>86736</v>
+        <v>82963</v>
       </c>
       <c r="D115" t="n">
-        <v>19.69</v>
+        <v>434.28</v>
       </c>
       <c r="E115" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F115" t="n">
-        <v>624</v>
+        <v>1839</v>
       </c>
       <c r="G115" t="n">
-        <v>232.12</v>
+        <v>336.63</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J115" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1879</v>
+      </c>
+      <c r="L115" t="n">
+        <v>119</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.563</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.062</t>
+          <t>2026-05-29 09:43:08.586</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779422087179</v>
+        <v>1780022586890</v>
       </c>
       <c r="C116" t="n">
-        <v>86376</v>
+        <v>83371</v>
       </c>
       <c r="D116" t="n">
-        <v>-341.3</v>
+        <v>820.5599999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F116" t="n">
-        <v>624</v>
+        <v>1839</v>
       </c>
       <c r="G116" t="n">
-        <v>232.12</v>
+        <v>336.63</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J116" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1694</v>
+      </c>
+      <c r="L116" t="n">
+        <v>102</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.319</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.371</t>
+          <t>2026-05-29 09:43:08.587</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779422087380</v>
+        <v>1780022587090</v>
       </c>
       <c r="C117" t="n">
-        <v>86601</v>
+        <v>83469</v>
       </c>
       <c r="D117" t="n">
-        <v>-99.23</v>
+        <v>877.53</v>
       </c>
       <c r="E117" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F117" t="n">
-        <v>624</v>
+        <v>1839</v>
       </c>
       <c r="G117" t="n">
-        <v>232.12</v>
+        <v>336.63</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J117" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1496</v>
+      </c>
+      <c r="L117" t="n">
+        <v>119</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.372</t>
+          <t>2026-05-29 09:43:08.588</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779422087582</v>
+        <v>1780022587290</v>
       </c>
       <c r="C118" t="n">
-        <v>86900</v>
+        <v>83730</v>
       </c>
       <c r="D118" t="n">
-        <v>204.73</v>
+        <v>1094.66</v>
       </c>
       <c r="E118" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F118" t="n">
-        <v>725</v>
+        <v>1839</v>
       </c>
       <c r="G118" t="n">
-        <v>229.28</v>
+        <v>336.63</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1297</v>
+      </c>
+      <c r="L118" t="n">
+        <v>117</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.927</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.769</t>
+          <t>2026-05-29 09:43:08.589</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779422087783</v>
+        <v>1780022587490</v>
       </c>
       <c r="C119" t="n">
-        <v>87102</v>
+        <v>83010</v>
       </c>
       <c r="D119" t="n">
-        <v>396.49</v>
+        <v>319.92</v>
       </c>
       <c r="E119" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F119" t="n">
-        <v>725</v>
+        <v>1839</v>
       </c>
       <c r="G119" t="n">
-        <v>229.28</v>
+        <v>336.63</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1098</v>
+      </c>
+      <c r="L119" t="n">
+        <v>117</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.853</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:45.770</t>
+          <t>2026-05-29 09:43:08.794</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779422087985</v>
+        <v>1780022587709</v>
       </c>
       <c r="C120" t="n">
-        <v>86543</v>
+        <v>82793</v>
       </c>
       <c r="D120" t="n">
-        <v>-182.33</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F120" t="n">
-        <v>725</v>
+        <v>1839</v>
       </c>
       <c r="G120" t="n">
-        <v>229.28</v>
+        <v>336.63</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L120" t="n">
+        <v>119</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.012</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:46.178</t>
+          <t>2026-05-29 09:43:08.834</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779422088186</v>
+        <v>1780022587909</v>
       </c>
       <c r="C121" t="n">
-        <v>86807</v>
+        <v>82957</v>
       </c>
       <c r="D121" t="n">
-        <v>90.78</v>
+        <v>246.58</v>
       </c>
       <c r="E121" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F121" t="n">
-        <v>725</v>
+        <v>1839</v>
       </c>
       <c r="G121" t="n">
-        <v>229.28</v>
+        <v>336.63</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>924</v>
+      </c>
+      <c r="L121" t="n">
+        <v>115</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.126</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:46.179</t>
+          <t>2026-05-29 09:43:09.521</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779422088387</v>
+        <v>1780022588109</v>
       </c>
       <c r="C122" t="n">
-        <v>87114</v>
+        <v>83114</v>
       </c>
       <c r="D122" t="n">
-        <v>393.25</v>
+        <v>391.25</v>
       </c>
       <c r="E122" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F122" t="n">
-        <v>826</v>
+        <v>1839</v>
       </c>
       <c r="G122" t="n">
-        <v>227.41</v>
+        <v>336.63</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1411</v>
+      </c>
+      <c r="L122" t="n">
+        <v>115</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.028</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:46.721</t>
+          <t>2026-05-29 09:43:09.522</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779422088589</v>
+        <v>1780022588309</v>
       </c>
       <c r="C123" t="n">
-        <v>87285</v>
+        <v>83279</v>
       </c>
       <c r="D123" t="n">
-        <v>544.58</v>
+        <v>536.6900000000001</v>
       </c>
       <c r="E123" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F123" t="n">
-        <v>826</v>
+        <v>1839</v>
       </c>
       <c r="G123" t="n">
-        <v>227.41</v>
+        <v>336.63</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L123" t="n">
+        <v>113</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.061</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:46.722</t>
+          <t>2026-05-29 09:43:10.253</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779422088790</v>
+        <v>1780022588510</v>
       </c>
       <c r="C124" t="n">
-        <v>86724</v>
+        <v>83442</v>
       </c>
       <c r="D124" t="n">
-        <v>-43.65</v>
+        <v>672.86</v>
       </c>
       <c r="E124" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F124" t="n">
-        <v>826</v>
+        <v>2059</v>
       </c>
       <c r="G124" t="n">
-        <v>227.41</v>
+        <v>336.63</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1742</v>
+      </c>
+      <c r="L124" t="n">
+        <v>107</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.147</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:47.008</t>
+          <t>2026-05-29 09:43:10.256</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779422088992</v>
+        <v>1780022588709</v>
       </c>
       <c r="C125" t="n">
-        <v>86896</v>
+        <v>82622</v>
       </c>
       <c r="D125" t="n">
-        <v>130.54</v>
+        <v>-180.79</v>
       </c>
       <c r="E125" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F125" t="n">
-        <v>826</v>
+        <v>2059</v>
       </c>
       <c r="G125" t="n">
-        <v>227.41</v>
+        <v>336.63</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1545</v>
+      </c>
+      <c r="L125" t="n">
+        <v>109</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.338</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:47.009</t>
+          <t>2026-05-29 09:43:10.476</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779422089193</v>
+        <v>1780022588910</v>
       </c>
       <c r="C126" t="n">
-        <v>87102</v>
+        <v>81811</v>
       </c>
       <c r="D126" t="n">
-        <v>330.01</v>
+        <v>-982.75</v>
       </c>
       <c r="E126" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F126" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G126" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1565</v>
+      </c>
+      <c r="L126" t="n">
+        <v>109</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:47.407</t>
+          <t>2026-05-29 09:43:10.508</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779422089394</v>
+        <v>1780022589109</v>
       </c>
       <c r="C127" t="n">
-        <v>87180</v>
+        <v>82585</v>
       </c>
       <c r="D127" t="n">
-        <v>391.51</v>
+        <v>-159.61</v>
       </c>
       <c r="E127" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F127" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G127" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1398</v>
+      </c>
+      <c r="L127" t="n">
+        <v>112</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:47.407</t>
+          <t>2026-05-29 09:43:10.516</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779422089596</v>
+        <v>1780022589328</v>
       </c>
       <c r="C128" t="n">
-        <v>86866</v>
+        <v>82894</v>
       </c>
       <c r="D128" t="n">
-        <v>57.93</v>
+        <v>157.37</v>
       </c>
       <c r="E128" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F128" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G128" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1187</v>
+      </c>
+      <c r="L128" t="n">
+        <v>107</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.258</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.089</t>
+          <t>2026-05-29 09:43:10.569</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779422089797</v>
+        <v>1780022589528</v>
       </c>
       <c r="C129" t="n">
-        <v>86285</v>
+        <v>82607</v>
       </c>
       <c r="D129" t="n">
-        <v>-525.96</v>
+        <v>-137.5</v>
       </c>
       <c r="E129" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F129" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G129" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L129" t="n">
+        <v>131</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.094</t>
+          <t>2026-05-29 09:43:11.027</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779422089999</v>
+        <v>1780022589728</v>
       </c>
       <c r="C130" t="n">
-        <v>86555</v>
+        <v>82412</v>
       </c>
       <c r="D130" t="n">
-        <v>-229.66</v>
+        <v>-325.62</v>
       </c>
       <c r="E130" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F130" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G130" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1298</v>
+      </c>
+      <c r="L130" t="n">
+        <v>108</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.361</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.454</t>
+          <t>2026-05-29 09:43:11.029</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779422090200</v>
+        <v>1780022589928</v>
       </c>
       <c r="C131" t="n">
-        <v>86037</v>
+        <v>82333</v>
       </c>
       <c r="D131" t="n">
-        <v>-736.1799999999999</v>
+        <v>-388.34</v>
       </c>
       <c r="E131" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F131" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G131" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L131" t="n">
+        <v>118</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.143</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.472</t>
+          <t>2026-05-29 09:43:11.667</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779422090401</v>
+        <v>1780022590129</v>
       </c>
       <c r="C132" t="n">
-        <v>85888</v>
+        <v>82333</v>
       </c>
       <c r="D132" t="n">
-        <v>-848.37</v>
+        <v>-368.93</v>
       </c>
       <c r="E132" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F132" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G132" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="J132" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1537</v>
+      </c>
+      <c r="L132" t="n">
+        <v>149</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.473</t>
+          <t>2026-05-29 09:43:11.668</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779422090603</v>
+        <v>1780022590328</v>
       </c>
       <c r="C133" t="n">
-        <v>85637</v>
+        <v>82443</v>
       </c>
       <c r="D133" t="n">
-        <v>-1056.95</v>
+        <v>-240.48</v>
       </c>
       <c r="E133" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F133" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G133" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1339</v>
+      </c>
+      <c r="L133" t="n">
+        <v>129</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.850</t>
+          <t>2026-05-29 09:43:11.669</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779422090804</v>
+        <v>1780022590528</v>
       </c>
       <c r="C134" t="n">
-        <v>85657</v>
+        <v>82557</v>
       </c>
       <c r="D134" t="n">
-        <v>-984.11</v>
+        <v>-114.45</v>
       </c>
       <c r="E134" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F134" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G134" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L134" t="n">
+        <v>148</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:48.851</t>
+          <t>2026-05-29 09:43:11.670</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779422091006</v>
+        <v>1780022590728</v>
       </c>
       <c r="C135" t="n">
-        <v>85425</v>
+        <v>82413</v>
       </c>
       <c r="D135" t="n">
-        <v>-1166.9</v>
+        <v>-252.73</v>
       </c>
       <c r="E135" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F135" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G135" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>942</v>
+      </c>
+      <c r="L135" t="n">
+        <v>106</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.707</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:49.242</t>
+          <t>2026-05-29 09:43:12.062</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779422091207</v>
+        <v>1780022590947</v>
       </c>
       <c r="C136" t="n">
-        <v>85563</v>
+        <v>82379</v>
       </c>
       <c r="D136" t="n">
-        <v>-970.5599999999999</v>
+        <v>-274.1</v>
       </c>
       <c r="E136" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F136" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G136" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L136" t="n">
+        <v>114</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.522</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:49.243</t>
+          <t>2026-05-29 09:43:12.121</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779422091408</v>
+        <v>1780022591147</v>
       </c>
       <c r="C137" t="n">
-        <v>85658</v>
+        <v>82037</v>
       </c>
       <c r="D137" t="n">
-        <v>-827.03</v>
+        <v>-602.39</v>
       </c>
       <c r="E137" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F137" t="n">
-        <v>866</v>
+        <v>2059</v>
       </c>
       <c r="G137" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K137" t="n">
+        <v>973</v>
+      </c>
+      <c r="L137" t="n">
+        <v>111</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:49.828</t>
+          <t>2026-05-29 09:43:12.134</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779422091610</v>
+        <v>1780022591347</v>
       </c>
       <c r="C138" t="n">
-        <v>85428</v>
+        <v>81967</v>
       </c>
       <c r="D138" t="n">
-        <v>-1015.68</v>
+        <v>-642.27</v>
       </c>
       <c r="E138" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F138" t="n">
-        <v>2296</v>
+        <v>2059</v>
       </c>
       <c r="G138" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>786</v>
+      </c>
+      <c r="L138" t="n">
+        <v>132</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.287</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:49.829</t>
+          <t>2026-05-29 09:43:12.496</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779422091811</v>
+        <v>1780022591547</v>
       </c>
       <c r="C139" t="n">
-        <v>85965</v>
+        <v>82097</v>
       </c>
       <c r="D139" t="n">
-        <v>-427.89</v>
+        <v>-480.16</v>
       </c>
       <c r="E139" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F139" t="n">
-        <v>2296</v>
+        <v>2059</v>
       </c>
       <c r="G139" t="n">
-        <v>154.7</v>
+        <v>336.63</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K139" t="n">
+        <v>948</v>
+      </c>
+      <c r="L139" t="n">
+        <v>121</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.105</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.220</t>
+          <t>2026-05-29 09:43:12.502</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779422092013</v>
+        <v>1780022591747</v>
       </c>
       <c r="C140" t="n">
-        <v>86071</v>
+        <v>82234</v>
       </c>
       <c r="D140" t="n">
-        <v>-300.5</v>
+        <v>-319.15</v>
       </c>
       <c r="E140" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F140" t="n">
-        <v>383</v>
+        <v>2059</v>
       </c>
       <c r="G140" t="n">
-        <v>159.51</v>
+        <v>336.63</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>754</v>
+      </c>
+      <c r="L140" t="n">
+        <v>107</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.282</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.310</t>
+          <t>2026-05-29 09:43:12.990</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779422092214</v>
+        <v>1780022591947</v>
       </c>
       <c r="C141" t="n">
-        <v>86125</v>
+        <v>82487</v>
       </c>
       <c r="D141" t="n">
-        <v>-231.47</v>
+        <v>-50.19</v>
       </c>
       <c r="E141" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F141" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G141" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L141" t="n">
+        <v>120</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.636</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.341</t>
+          <t>2026-05-29 09:43:12.991</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779422092415</v>
+        <v>1780022592147</v>
       </c>
       <c r="C142" t="n">
-        <v>86378</v>
+        <v>82664</v>
       </c>
       <c r="D142" t="n">
-        <v>33.1</v>
+        <v>129.32</v>
       </c>
       <c r="E142" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F142" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G142" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>843</v>
+      </c>
+      <c r="L142" t="n">
+        <v>106</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.833</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.482</t>
+          <t>2026-05-29 09:43:13.287</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779422092617</v>
+        <v>1780022592366</v>
       </c>
       <c r="C143" t="n">
-        <v>86642</v>
+        <v>82704</v>
       </c>
       <c r="D143" t="n">
-        <v>295.45</v>
+        <v>162.85</v>
       </c>
       <c r="E143" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F143" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G143" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K143" t="n">
+        <v>920</v>
+      </c>
+      <c r="L143" t="n">
+        <v>114</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.364</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.978</t>
+          <t>2026-05-29 09:43:13.290</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779422092818</v>
+        <v>1780022592566</v>
       </c>
       <c r="C144" t="n">
-        <v>87064</v>
+        <v>82440</v>
       </c>
       <c r="D144" t="n">
-        <v>702.67</v>
+        <v>-109.29</v>
       </c>
       <c r="E144" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F144" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G144" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K144" t="n">
+        <v>723</v>
+      </c>
+      <c r="L144" t="n">
+        <v>131</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.844</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:50.979</t>
+          <t>2026-05-29 09:43:13.810</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779422093020</v>
+        <v>1780022592766</v>
       </c>
       <c r="C145" t="n">
-        <v>86537</v>
+        <v>82360</v>
       </c>
       <c r="D145" t="n">
-        <v>140.54</v>
+        <v>-183.83</v>
       </c>
       <c r="E145" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F145" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G145" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L145" t="n">
+        <v>125</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.794</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:51.290</t>
+          <t>2026-05-29 09:43:13.818</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779422093221</v>
+        <v>1780022592966</v>
       </c>
       <c r="C146" t="n">
-        <v>86839</v>
+        <v>82683</v>
       </c>
       <c r="D146" t="n">
-        <v>435.51</v>
+        <v>148.36</v>
       </c>
       <c r="E146" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F146" t="n">
-        <v>383</v>
+        <v>1279</v>
       </c>
       <c r="G146" t="n">
-        <v>159.51</v>
+        <v>291.72</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>850</v>
+      </c>
+      <c r="L146" t="n">
+        <v>117</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1.978</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:51.291</t>
+          <t>2026-05-29 09:43:14.112</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779422093422</v>
+        <v>1780022593166</v>
       </c>
       <c r="C147" t="n">
-        <v>87233</v>
+        <v>83398</v>
       </c>
       <c r="D147" t="n">
-        <v>807.74</v>
+        <v>855.95</v>
       </c>
       <c r="E147" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F147" t="n">
-        <v>1430</v>
+        <v>1299</v>
       </c>
       <c r="G147" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K147" t="n">
+        <v>944</v>
+      </c>
+      <c r="L147" t="n">
+        <v>119</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:51.804</t>
+          <t>2026-05-29 09:43:14.157</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779422093624</v>
+        <v>1780022593366</v>
       </c>
       <c r="C148" t="n">
-        <v>87245</v>
+        <v>83471</v>
       </c>
       <c r="D148" t="n">
-        <v>779.35</v>
+        <v>886.15</v>
       </c>
       <c r="E148" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F148" t="n">
-        <v>1430</v>
+        <v>1299</v>
       </c>
       <c r="G148" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K148" t="n">
+        <v>790</v>
+      </c>
+      <c r="L148" t="n">
+        <v>109</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.825</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:51.805</t>
+          <t>2026-05-29 09:43:14.393</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1779422093825</v>
+        <v>1780022593566</v>
       </c>
       <c r="C149" t="n">
-        <v>86938</v>
+        <v>82554</v>
       </c>
       <c r="D149" t="n">
-        <v>433.38</v>
+        <v>-75.16</v>
       </c>
       <c r="E149" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F149" t="n">
-        <v>1430</v>
+        <v>1299</v>
       </c>
       <c r="G149" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K149" t="n">
+        <v>826</v>
+      </c>
+      <c r="L149" t="n">
+        <v>116</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.796</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:52.193</t>
+          <t>2026-05-29 09:43:14.879</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1779422094027</v>
+        <v>1780022593766</v>
       </c>
       <c r="C150" t="n">
-        <v>87216</v>
+        <v>82812</v>
       </c>
       <c r="D150" t="n">
-        <v>689.71</v>
+        <v>186.6</v>
       </c>
       <c r="E150" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F150" t="n">
-        <v>1430</v>
+        <v>1299</v>
       </c>
       <c r="G150" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1112</v>
+      </c>
+      <c r="L150" t="n">
+        <v>111</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.046</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:52.199</t>
+          <t>2026-05-29 09:43:14.881</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1779422094228</v>
+        <v>1780022593985</v>
       </c>
       <c r="C151" t="n">
-        <v>87602</v>
+        <v>82558</v>
       </c>
       <c r="D151" t="n">
-        <v>1041.23</v>
+        <v>-76.73</v>
       </c>
       <c r="E151" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F151" t="n">
-        <v>785</v>
+        <v>1299</v>
       </c>
       <c r="G151" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I151" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K151" t="n">
+        <v>895</v>
+      </c>
+      <c r="L151" t="n">
+        <v>107</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1.609</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:52.200</t>
+          <t>2026-05-29 09:43:15.109</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1779422094429</v>
+        <v>1780022594186</v>
       </c>
       <c r="C152" t="n">
-        <v>87075</v>
+        <v>82610</v>
       </c>
       <c r="D152" t="n">
-        <v>462.17</v>
+        <v>-20.89</v>
       </c>
       <c r="E152" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F152" t="n">
-        <v>785</v>
+        <v>1299</v>
       </c>
       <c r="G152" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I152" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J152" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K152" t="n">
+        <v>922</v>
+      </c>
+      <c r="L152" t="n">
+        <v>107</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.047</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:52.521</t>
+          <t>2026-05-29 09:43:15.111</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1779422094631</v>
+        <v>1780022594385</v>
       </c>
       <c r="C153" t="n">
-        <v>87449</v>
+        <v>82326</v>
       </c>
       <c r="D153" t="n">
-        <v>813.0599999999999</v>
+        <v>-303.85</v>
       </c>
       <c r="E153" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F153" t="n">
-        <v>785</v>
+        <v>1299</v>
       </c>
       <c r="G153" t="n">
-        <v>279.66</v>
+        <v>297.05</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I153" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J153" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K153" t="n">
+        <v>725</v>
+      </c>
+      <c r="L153" t="n">
+        <v>107</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1.165</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:52.928</t>
+          <t>2026-05-29 09:43:15.634</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1779422094832</v>
+        <v>1780022594585</v>
       </c>
       <c r="C154" t="n">
-        <v>87771</v>
+        <v>82612</v>
       </c>
       <c r="D154" t="n">
-        <v>1094.41</v>
+        <v>-2.66</v>
       </c>
       <c r="E154" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F154" t="n">
-        <v>685</v>
+        <v>1299</v>
       </c>
       <c r="G154" t="n">
-        <v>263.68</v>
+        <v>297.05</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:54:52.929</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1779422095034</v>
-      </c>
-      <c r="C155" t="n">
-        <v>87583</v>
-      </c>
-      <c r="D155" t="n">
-        <v>851.6799999999999</v>
-      </c>
-      <c r="E155" t="n">
-        <v>90</v>
-      </c>
-      <c r="F155" t="n">
-        <v>685</v>
-      </c>
-      <c r="G155" t="n">
-        <v>263.68</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:54:53.354</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>1779422095235</v>
-      </c>
-      <c r="C156" t="n">
-        <v>87479</v>
-      </c>
-      <c r="D156" t="n">
-        <v>705.1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>90</v>
-      </c>
-      <c r="F156" t="n">
-        <v>685</v>
-      </c>
-      <c r="G156" t="n">
-        <v>263.68</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I154" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J154" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1047</v>
+      </c>
+      <c r="L154" t="n">
+        <v>116</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>
